--- a/artfynd/A 40083-2023 artfynd.xlsx
+++ b/artfynd/A 40083-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,54 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120595756</v>
+        <v>120595908</v>
       </c>
       <c r="B2" t="n">
-        <v>97010</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Södra Vi, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548101</v>
+        <v>548683</v>
       </c>
       <c r="R2" t="n">
-        <v>6399925</v>
+        <v>6399776</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,12 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-09</t>
+          <t>2024-05-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120595735</v>
+        <v>120595734</v>
       </c>
       <c r="B3" t="n">
-        <v>97010</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548271</v>
+        <v>548241</v>
       </c>
       <c r="R3" t="n">
-        <v>6399988</v>
+        <v>6399958</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120595736</v>
+        <v>120595735</v>
       </c>
       <c r="B4" t="n">
-        <v>97010</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548276</v>
+        <v>548271</v>
       </c>
       <c r="R4" t="n">
-        <v>6399978</v>
+        <v>6399988</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,15 +975,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120595734</v>
+        <v>120595736</v>
       </c>
       <c r="B5" t="n">
-        <v>97010</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548241</v>
+        <v>548276</v>
       </c>
       <c r="R5" t="n">
-        <v>6399958</v>
+        <v>6399978</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1080,6 +1069,588 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120595738</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Södra Vi, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>548651</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6399897</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Södra Vi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Ieva Mardega, Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120595739</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södra Vi, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>548662</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6399857</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Södra Vi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ieva Mardega, Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120595749</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södra Vi, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>548667</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6399828</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Södra Vi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ieva Mardega, Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120595750</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Södra Vi, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>548627</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6399929</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Södra Vi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Ieva Mardega, Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120595751</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Södra Vi, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>548094</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6399901</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Södra Vi</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-06-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ieva Mardega, Louise Lindroth</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120595756</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Södra Vi, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>548101</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6399925</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Södra Vi</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ieva Mardega</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40083-2023 artfynd.xlsx
+++ b/artfynd/A 40083-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595908</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595734</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595735</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595736</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1166,6 +1191,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595738</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1263,6 +1293,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595739</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1360,6 +1395,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595749</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1457,6 +1497,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595750</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1554,6 +1599,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595751</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1651,8 +1701,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120595756</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>